--- a/output/pdf_financials_xlsx/CPS.xlsx
+++ b/output/pdf_financials_xlsx/CPS.xlsx
@@ -4712,25 +4712,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.813311</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.113957</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.921903</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.921903</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.498938</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.847241</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.493883</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -10048,7 +10048,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -11028,7 +11032,11 @@
           <t>Warrant reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>1.314373</v>
       </c>
@@ -11103,7 +11111,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -12541,7 +12553,11 @@
           <t>Share-based payments reserve (Note 15)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>0.498938</v>
       </c>

--- a/output/pdf_financials_xlsx/CPS.xlsx
+++ b/output/pdf_financials_xlsx/CPS.xlsx
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-2e-05</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005012</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002599</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002599</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -947,25 +947,25 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.06794600000000001</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015157</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005431</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.037731</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.164426</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06826699999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.053836</v>
       </c>
     </row>
     <row r="13">
@@ -1673,16 +1673,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.767919</v>
+        <v>-0.767899</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.22714</v>
+        <v>-1.222128</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.280923</v>
+        <v>-2.278324</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.610324</v>
+        <v>-0.607725</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.552638</v>
@@ -1691,25 +1691,25 @@
         <v>-3.091365</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-13.511154</v>
+        <v>-13.5791</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.116187</v>
+        <v>-1.10103</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.499782</v>
+        <v>-2.494351</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.383121</v>
+        <v>-5.34539</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-8.534393</v>
+        <v>-8.369967000000001</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.158983</v>
+        <v>-4.090716</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.375836</v>
+        <v>-3.322</v>
       </c>
     </row>
     <row r="28">
@@ -1765,16 +1765,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.767919</v>
+        <v>-0.767899</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.22714</v>
+        <v>-1.222128</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.280923</v>
+        <v>-2.278324</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.610324</v>
+        <v>-0.607725</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.552638</v>
@@ -1783,25 +1783,25 @@
         <v>-3.091365</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-13.505649</v>
+        <v>-13.573595</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.074944</v>
+        <v>-1.059787</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.48357</v>
+        <v>-2.478139</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.357782</v>
+        <v>-5.320051</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-8.485277</v>
+        <v>-8.320850999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.113073</v>
+        <v>-4.044806</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.326455</v>
+        <v>-3.272619</v>
       </c>
     </row>
     <row r="30">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-79.46507974643775</v>
+        <v>-78.34460071337486</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2004,19 +2004,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.055491</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.987883</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000781</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.015761</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.534981</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>10.547859</v>
@@ -2096,19 +2096,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.055491</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.987883</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000781</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.015761</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.534981</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>10.547859</v>
@@ -2648,19 +2648,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.075626</v>
+        <v>0.020135</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.098071</v>
+        <v>0.110188</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.038788</v>
+        <v>0.038007</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.039661</v>
+        <v>0.0239</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.604859</v>
+        <v>0.069878</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.075443</v>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
@@ -24713,7 +24713,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -26441,7 +26441,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -30239,7 +30239,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E296" s="5" t="n">
@@ -32167,7 +32167,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">

--- a/output/pdf_financials_xlsx/CPS.xlsx
+++ b/output/pdf_financials_xlsx/CPS.xlsx
@@ -1008,10 +1008,10 @@
         <v>-0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.7599900000000001</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.845988</v>
       </c>
     </row>
     <row r="14">
@@ -1706,10 +1706,10 @@
         <v>-8.369967000000001</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.090716</v>
+        <v>-3.330726</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.322</v>
+        <v>-2.476012</v>
       </c>
     </row>
     <row r="28">
@@ -1798,10 +1798,10 @@
         <v>-8.320850999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.044806</v>
+        <v>-3.284816</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.272619</v>
+        <v>-2.426631</v>
       </c>
     </row>
     <row r="30">
@@ -22886,7 +22886,11 @@
           <t>Net finance costs 14</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -24873,7 +24877,11 @@
           <t>Total net finance costs</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CPS.xlsx
+++ b/output/pdf_financials_xlsx/CPS.xlsx
@@ -7613,7 +7613,11 @@
           <t>Lease liabilities 7</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -8770,7 +8774,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -14303,7 +14311,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -15427,7 +15439,11 @@
           <t>Proceeds from private placement 10</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -16233,7 +16249,11 @@
           <t>Proceeds from private placement 12</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -23036,7 +23056,11 @@
           <t>Income tax (recovery) expense 15</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -25250,7 +25274,11 @@
           <t>Income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -28264,7 +28292,11 @@
           <t>Income tax (recovery) expense 21</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
